--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SAP S/4 Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f609856527b5e2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=20c3803f586deedc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>SAP S/4 Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lexington Capital Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Port Jefferson Station, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb6c8151bb3d9891</t>
+          <t>https://www.indeed.com/viewjob?jk=f609856527b5e2b8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Lexington Capital Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Port Jefferson Station, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=eb6c8151bb3d9891</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote Available)</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,147 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Data Engineer (Remote Available)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Vanderbilt University Medical Center</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Senior .NET Developer (Oracle Platform Integration)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Qogen, LLC</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
         <v>11.1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer - Machine Learning</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trimble</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MLOps, Azure DevOps, Git, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4fa376cb1aac719</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote Available)</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center</t>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SAP S/4 Solution Architect</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lexington Capital Holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Port Jefferson Station, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f609856527b5e2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb6c8151bb3d9891</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lexington Capital Holdings</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Port Jefferson Station, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb6c8151bb3d9891</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior .NET Developer (Oracle Platform Integration)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qogen, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,77 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior .NET Developer (Oracle Platform Integration)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Qogen, LLC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer - Machine Learning</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Trimble</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Westminster, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MLOps, Azure DevOps, Git, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4fa376cb1aac719</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -666,80 +666,990 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Helena, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>North Andover, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Medford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Troy, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Middletown, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Senior .NET Developer (Oracle Platform Integration)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Qogen, LLC</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D35" t="n">
         <v>11.1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
         </is>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Qogen, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,87 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Qogen, LLC</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>.NET Architect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,69 +1606,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qogen, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,50 +1676,85 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Qogen, LLC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>.NET Architect</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D38" t="n">
         <v>10.4</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qogen, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,40 +1721,110 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Qogen, LLC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>.NET Architect</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D40" t="n">
         <v>10.4</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lexington Capital Holdings</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Port Jefferson Station, NY, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb6c8151bb3d9891</t>
+          <t>https://www.indeed.com/viewjob?jk=f0033abf803ced42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Lexington Capital Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Port Jefferson Station, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=eb6c8151bb3d9891</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
+          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Helena, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
+          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Helena, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
+          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
+          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
+          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Troy, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
+          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
+          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Troy, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
+          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
+          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
+          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
+          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Middletown, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Middletown, CT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1576,37 +1576,37 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Qogen, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,40 +1791,145 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lennar</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Qogen, LLC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>.NET Architect</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D43" t="n">
         <v>10.4</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c3803f586deedc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed0702643990e72</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>West Lake, LA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0033abf803ced42</t>
+          <t>https://www.indeed.com/viewjob?jk=51d2af5d54195fff</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lexington Capital Holdings</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Port Jefferson Station, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,137 +566,137 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb6c8151bb3d9891</t>
+          <t>https://www.indeed.com/viewjob?jk=20c3803f586deedc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=83f72088600a0d11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Data Engineer with Python-5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d7fd6b3a45530d9c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Lexington Capital Holdings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Port Jefferson Station, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb6c8151bb3d9891</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Helena, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,94 +916,94 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
+          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Troy, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
+          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
+          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Helena, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
+          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
+          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
+          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Middletown, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Troy, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1646,37 +1646,37 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,75 +1861,600 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Qogen, LLC</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Middletown, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Medica Services Company LLC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cloud DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Regions Financial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Hoover, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Bentley Systems</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Exton, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Lennar</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Qogen, LLC</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FiveTran Administrator / Data Integration Engineer-2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Lebanon, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8049ed1c967550ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>.NET Architect</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D58" t="n">
         <v>10.4</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-4</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f72088600a0d11</t>
+          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer with Python-5</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fd6b3a45530d9c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lexington Capital Holdings</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Port Jefferson Station, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb6c8151bb3d9891</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,199 +811,199 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Helena, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
+          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
+          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Helena, MO, US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
+          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
+          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Troy, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
+          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
+          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Troy, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
+          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
+          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
+          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
+          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Middletown, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
+          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
+          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Middletown, CT, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1961,37 +1961,37 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,49 +2176,49 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior .NET Developer (Oracle Platform Integration)</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Qogen, LLC</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer-2</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2350,111 +2350,6 @@
         </is>
       </c>
       <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8049ed1c967550ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Azure Security Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Azure Security Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>.NET Architect</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,29 +976,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Alkami Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, SQS, RDS, Kafka, SQL Server, MongoDB, DynamoDB, CI/CD, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0117a3b871784ee4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Helena, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
+          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
+          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Helena, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
+          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
+          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Troy, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
+          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Troy, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
+          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
+          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
+          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
+          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Middletown, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Middletown, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1961,37 +1961,37 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=89ff6f25f9a6803e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,40 +2316,390 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e14a2c939b76bd2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Lennar</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Solutions Engineer II - Networking</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Innovative Systems</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>.NET Architect</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D65" t="n">
         <v>10.4</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kennesaw State University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Medallion Architecture, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab4ea66cd88f5a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
+          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Engineer - MLOps &amp; Production AI Systems - Remote or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8efb3901b9a2f678</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,77 +941,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Sr. Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alkami Technology</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Kafka, SQL Server, MongoDB, DynamoDB, CI/CD, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0117a3b871784ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf76acfd2510ec</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,54 +1056,54 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,38 +1112,38 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Alkami Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Kafka, SQL Server, MongoDB, DynamoDB, CI/CD, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
+          <t>https://www.indeed.com/viewjob?jk=0117a3b871784ee4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Helena, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
+          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Helena, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
+          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
+          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Troy, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
+          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
+          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
+          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Troy, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
+          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
+          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
+          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Middletown, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2066,37 +2066,37 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Middletown, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ff6f25f9a6803e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. DevOps Engineer AWS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=47bbf34a2d6b1efb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,49 +2386,49 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14a2c939b76bd2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2442,11 +2442,11 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=89ff6f25f9a6803e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2547,11 +2547,11 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e14a2c939b76bd2f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,15 +2691,260 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Innovative Systems</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>.NET Architect</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Administrator Engineer (Remote Position)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Faculty Physicians Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, Athena, RDS, Azure, Data Factory, GCP, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8806e64c85174a</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer - MLOps &amp; Production AI Systems - Remote or Hybrid in MN/DC</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efb3901b9a2f678</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Oracle, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=e09691593f63d9bf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>Senior AI/ML Engineer - MLOps &amp; Production AI Systems - Remote or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=8efb3901b9a2f678</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Java Full Stack Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf76acfd2510ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,29 +1081,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf76acfd2510ec</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alkami Technology</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,38 +1182,38 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Kafka, SQL Server, MongoDB, DynamoDB, CI/CD, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0117a3b871784ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Alkami Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, SQS, RDS, Kafka, SQL Server, MongoDB, DynamoDB, CI/CD, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0117a3b871784ee4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
+          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Helena, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
+          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Helena, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
+          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
+          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
+          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Troy, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
+          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
+          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Troy, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
+          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
+          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
+          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
+          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Middletown, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Middletown, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2241,37 +2241,37 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer AWS</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bbf34a2d6b1efb</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ff6f25f9a6803e</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=89ff6f25f9a6803e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Sr. DevOps Engineer AWS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=47bbf34a2d6b1efb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14a2c939b76bd2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=e14a2c939b76bd2f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,15 +2936,295 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a7425dae5000454</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Innovative Systems</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Nexxen</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=900fcf3171128995</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>.NET Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c86c7409f7392c29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer - Wixom, MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
+          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Administrator Engineer (Remote Position)</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Faculty Physicians Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Data Factory, GCP, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8806e64c85174a</t>
+          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, PostgreSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb574f0ac8cc392</t>
         </is>
       </c>
     </row>
@@ -823,55 +823,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=f0033abf803ced42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Administrator Engineer (Remote Position)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Faculty Physicians Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Athena, RDS, Azure, Data Factory, GCP, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8806e64c85174a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Developer, IT Applications</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Oracle, Power BI, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09691593f63d9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer - MLOps &amp; Production AI Systems - Remote or Hybrid in MN/DC</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efb3901b9a2f678</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Java Full Stack Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf76acfd2510ec</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior AI/ML Engineer - MLOps &amp; Production AI Systems - Remote or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8efb3901b9a2f678</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Oracle, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e09691593f63d9bf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alkami Technology</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Kafka, SQL Server, MongoDB, DynamoDB, CI/CD, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0117a3b871784ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Sr. Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf76acfd2510ec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,94 +1441,94 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Helena, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>North Andover, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Alkami Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Kafka, SQL Server, MongoDB, DynamoDB, CI/CD, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=0117a3b871784ee4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Troy, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,89 +1966,89 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,116 +2057,116 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Sr. DevOps Engineer AWS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Middletown, CT, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=47bbf34a2d6b1efb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, Splunk, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+          <t>https://www.indeed.com/viewjob?jk=06d621813e7a1465</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, Splunk, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+          <t>https://www.indeed.com/viewjob?jk=63620fccee2f27a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DNV</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=052ff42df262f3f2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ff6f25f9a6803e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer AWS</t>
+          <t>Senior Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Integrated Specialty Coverages</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bbf34a2d6b1efb</t>
+          <t>https://www.indeed.com/viewjob?jk=9615cc9cb83785ce</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3091aa9276b5fecf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14a2c939b76bd2f</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=f2469be7cd2fcd5c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nexxen</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=900fcf3171128995</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7425dae5000454</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Site Reliability Engineer - Machine Learning</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MLOps, Azure DevOps, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=e4fa376cb1aac719</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Computershare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexxen</t>
+          <t>ISOD Limited</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,147 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900fcf3171128995</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Computershare</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>.NET Architect</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cf08e2c805e023</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-23.xlsx
+++ b/results/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Onsite Interviews (Denver)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c3803f586deedc</t>
+          <t>https://www.indeed.com/viewjob?jk=cb173fd010bc37d5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Specialist Software Engineering - Onsite Interviews (Denver)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kennesaw State University</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Medallion Architecture, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab4ea66cd88f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec5847773fc77b8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Kennesaw State University</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Medallion Architecture, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab4ea66cd88f5a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Intermediate Software Engineer - Onsite Interviews (Denver)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Azure, Data Factory, Event Hubs, Zookeeper, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb35aa20ed18f4d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c86c7409f7392c29</t>
+          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, PostgreSQL, Data Modeling, Power BI</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb574f0ac8cc392</t>
+          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0033abf803ced42</t>
+          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AWS Cloud Architect- US Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RELQ TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa07dcc1c5fe6d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Administrator Engineer (Remote Position)</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Faculty Physicians Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Data Factory, GCP, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8806e64c85174a</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer - MLOps &amp; Production AI Systems - Remote or Hybrid in MN/DC</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efb3901b9a2f678</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Developer, IT Applications</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Oracle, Power BI, Jenkins</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09691593f63d9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Java Full Stack Engineer</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf76acfd2510ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,29 +1466,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31ad70ec2232102</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Onsite Data Engineer Miami</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cypress, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior GenAI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Alkami Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Kafka, SQL Server, MongoDB, DynamoDB, CI/CD, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0117a3b871784ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=c14d8d29c2cadb59</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bbf34a2d6b1efb</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, Splunk, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d621813e7a1465</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, Splunk, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63620fccee2f27a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Integrated Specialty Coverages</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9615cc9cb83785ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3091aa9276b5fecf</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Computershare</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2469be7cd2fcd5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexxen</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900fcf3171128995</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,182 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer - Machine Learning</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Trimble</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Westminster, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, MLOps, Azure DevOps, Git, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4fa376cb1aac719</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Computershare</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>.NET Architect</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>ISOD Limited</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cf08e2c805e023</t>
         </is>
       </c>
     </row>
